--- a/jogos_2025-01-31.xlsx
+++ b/jogos_2025-01-31.xlsx
@@ -1159,19 +1159,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Umm al-Fahm</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1185,34 +1185,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>14.5</v>
+        <v>3.9</v>
       </c>
       <c r="M6" t="n">
-        <v>6.1</v>
+        <v>3.02</v>
       </c>
       <c r="N6" t="n">
-        <v>1.14</v>
+        <v>1.92</v>
       </c>
       <c r="O6" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1236,21 +1236,21 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
           <t>['90']</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
@@ -1258,10 +1258,10 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45688.41666666666</v>
@@ -1804,22 +1804,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1830,34 +1830,34 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="O11" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1869,31 +1869,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.89</v>
+        <v>1.62</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['45+4']</t>
+          <t>['37', '43']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>['45+3', '81']</t>
         </is>
       </c>
       <c r="AG11" t="n">
@@ -1903,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AJ11" t="n">
         <v>2.2</v>
@@ -1933,19 +1933,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Umm al-Fahm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1959,34 +1959,34 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.9</v>
+        <v>14.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.02</v>
+        <v>6.1</v>
       </c>
       <c r="N12" t="n">
-        <v>1.92</v>
+        <v>1.14</v>
       </c>
       <c r="O12" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2010,19 +2010,19 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>['90']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG12" t="n">
@@ -2032,10 +2032,10 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45688.41666666666</v>
@@ -2062,22 +2062,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -2088,34 +2088,34 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="M13" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -2127,31 +2127,31 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['37', '43']</t>
+          <t>['45+4']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['45+3', '81']</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AG13" t="n">
@@ -2161,7 +2161,7 @@
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AJ13" t="n">
         <v>2.2</v>
@@ -2707,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="M18" t="n">
-        <v>2.53</v>
+        <v>2.85</v>
       </c>
       <c r="N18" t="n">
-        <v>3.65</v>
+        <v>3.29</v>
       </c>
       <c r="O18" t="n">
         <v>3.25</v>
@@ -2751,65 +2751,65 @@
         <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="S18" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="T18" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U18" t="n">
         <v>1.2</v>
       </c>
       <c r="V18" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W18" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="X18" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['45+4']</t>
+          <t>['53', '88']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AI18" t="n">
         <v>1.91</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45688.45833333334</v>
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="M19" t="n">
-        <v>2.85</v>
+        <v>2.53</v>
       </c>
       <c r="N19" t="n">
-        <v>3.29</v>
+        <v>3.65</v>
       </c>
       <c r="O19" t="n">
         <v>3.25</v>
@@ -2880,65 +2880,65 @@
         <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="S19" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="T19" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U19" t="n">
         <v>1.2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W19" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="X19" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AA19" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['53', '88']</t>
+          <t>['45+4']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AI19" t="n">
         <v>1.91</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45688.45833333334</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.97</v>
+        <v>1.32</v>
       </c>
       <c r="M23" t="n">
-        <v>3.48</v>
+        <v>5.25</v>
       </c>
       <c r="N23" t="n">
-        <v>1.84</v>
+        <v>7.48</v>
       </c>
       <c r="O23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.63</v>
-      </c>
       <c r="T23" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="V23" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>3.15</v>
+        <v>5.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.96</v>
+        <v>1.37</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.76</v>
+        <v>2.85</v>
       </c>
       <c r="AA23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>3.5</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['43']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>['74']</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.62</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45688.54166666666</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,16 +3481,16 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Urooba</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
@@ -3499,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.25</v>
+        <v>3.97</v>
       </c>
       <c r="M24" t="n">
-        <v>6</v>
+        <v>3.48</v>
       </c>
       <c r="N24" t="n">
-        <v>8.5</v>
+        <v>1.84</v>
       </c>
       <c r="O24" t="n">
+        <v>4</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>1.62</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>7</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S24" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X24" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>['45+1', '58']</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['39']</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>4</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45688.54166666666</v>
@@ -3739,22 +3739,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Urooba</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="M26" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="N26" t="n">
-        <v>7.48</v>
+        <v>8.5</v>
       </c>
       <c r="O26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>7</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U26" t="n">
         <v>1.8</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S26" t="n">
-        <v>4</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.73</v>
       </c>
       <c r="V26" t="n">
         <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1', '58']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['12']</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.85</v>
+        <v>3.75</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45688.54166666666</v>
@@ -3997,22 +3997,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.13</v>
+        <v>1.81</v>
       </c>
       <c r="M28" t="n">
-        <v>3.27</v>
+        <v>3.59</v>
       </c>
       <c r="N28" t="n">
-        <v>3.46</v>
+        <v>4.29</v>
       </c>
       <c r="O28" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="P28" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
         <v>4.2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>2.57</v>
+        <v>2.9</v>
       </c>
       <c r="T28" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="U28" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="V28" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W28" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="X28" t="n">
-        <v>2.96</v>
+        <v>3.82</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AA28" t="n">
-        <v>4.12</v>
+        <v>3.06</v>
       </c>
       <c r="AB28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC28" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['6', '36', '55']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>['69']</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45688.58333333334</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,22 +4126,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="M29" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T29" t="n">
         <v>3.2</v>
       </c>
-      <c r="N29" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.54</v>
-      </c>
       <c r="U29" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W29" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="X29" t="n">
-        <v>3.88</v>
+        <v>2.96</v>
       </c>
       <c r="Y29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>['6', '36', '55']</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.71</v>
       </c>
-      <c r="Z29" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>['62']</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AI29" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45688.58333333334</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,25 +4255,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.81</v>
+        <v>2.7</v>
       </c>
       <c r="M30" t="n">
-        <v>3.59</v>
+        <v>3.42</v>
       </c>
       <c r="N30" t="n">
-        <v>4.29</v>
+        <v>2.48</v>
       </c>
       <c r="O30" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
         <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="U30" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V30" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
         <v>1.25</v>
       </c>
       <c r="X30" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AD30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>['35', '43', '90+11']</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>['40']</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ30" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>['89']</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>2.55</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45688.58333333334</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,25 +4384,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>3</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.7</v>
+        <v>2.19</v>
       </c>
       <c r="M31" t="n">
-        <v>3.42</v>
+        <v>3.32</v>
       </c>
       <c r="N31" t="n">
-        <v>2.48</v>
+        <v>3.09</v>
       </c>
       <c r="O31" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="P31" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T31" t="n">
         <v>3</v>
       </c>
-      <c r="R31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U31" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="V31" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W31" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="X31" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['35', '43', '90+11']</t>
+          <t>['58', '64', '70']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AI31" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45688.58333333334</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,16 +4513,16 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -4539,65 +4539,65 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="M32" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>3.09</v>
+        <v>3.47</v>
       </c>
       <c r="O32" t="n">
         <v>2.88</v>
       </c>
       <c r="P32" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="T32" t="n">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="U32" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="V32" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="X32" t="n">
-        <v>3.25</v>
+        <v>3.88</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['58', '64', '70']</t>
+          <t>['62']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AI32" t="n">
         <v>1.73</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45688.58333333334</v>
@@ -4642,22 +4642,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="M33" t="n">
-        <v>3.66</v>
+        <v>3.88</v>
       </c>
       <c r="N33" t="n">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="O33" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="P33" t="n">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.3</v>
+        <v>3.53</v>
       </c>
       <c r="R33" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="S33" t="n">
-        <v>3.2</v>
+        <v>3.64</v>
       </c>
       <c r="T33" t="n">
         <v>2.3</v>
       </c>
       <c r="U33" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="V33" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="X33" t="n">
-        <v>4.2</v>
+        <v>5.15</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.55</v>
+        <v>2.27</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>['44', '50']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['75', '84']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45688.60416666666</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,22 +4771,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="M34" t="n">
-        <v>3.88</v>
+        <v>2.89</v>
       </c>
       <c r="N34" t="n">
-        <v>2.93</v>
+        <v>4.69</v>
       </c>
       <c r="O34" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P34" t="n">
-        <v>2.51</v>
+        <v>1.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.53</v>
+        <v>5.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="S34" t="n">
-        <v>3.64</v>
+        <v>2.1</v>
       </c>
       <c r="T34" t="n">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="U34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI34" t="n">
         <v>1.62</v>
       </c>
-      <c r="V34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X34" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>['44', '50']</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>['75', '84']</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AJ34" t="n">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45688.60416666666</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,16 +4900,16 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="M35" t="n">
-        <v>2.89</v>
+        <v>3.66</v>
       </c>
       <c r="N35" t="n">
-        <v>4.69</v>
+        <v>2.85</v>
       </c>
       <c r="O35" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="P35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI35" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q35" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T35" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X35" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AJ35" t="n">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45688.60416666666</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,25 +5029,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.22</v>
+        <v>2.39</v>
       </c>
       <c r="M36" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O36" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="P36" t="n">
         <v>2.32</v>
       </c>
-      <c r="O36" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1.99</v>
-      </c>
       <c r="Q36" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="R36" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="S36" t="n">
-        <v>2.36</v>
+        <v>3.28</v>
       </c>
       <c r="T36" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="U36" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="V36" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="X36" t="n">
-        <v>2.8</v>
+        <v>3.86</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.22</v>
+        <v>1.8</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.56</v>
+        <v>1.91</v>
       </c>
       <c r="AA36" t="n">
-        <v>4.1</v>
+        <v>2.83</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.89</v>
+        <v>1.59</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>['35', '82', '90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="AI36" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45688.625</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,25 +5287,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.39</v>
+        <v>3.22</v>
       </c>
       <c r="M38" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N38" t="n">
-        <v>2.65</v>
+        <v>2.32</v>
       </c>
       <c r="O38" t="n">
-        <v>3.11</v>
+        <v>3.85</v>
       </c>
       <c r="P38" t="n">
-        <v>2.32</v>
+        <v>1.99</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="R38" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="S38" t="n">
-        <v>3.28</v>
+        <v>2.36</v>
       </c>
       <c r="T38" t="n">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="U38" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W38" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="X38" t="n">
-        <v>3.86</v>
+        <v>2.8</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.8</v>
+        <v>2.22</v>
       </c>
       <c r="Z38" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>['35', '82', '90+2']</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ38" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.96</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45688.625</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,109 +5416,109 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FC Schaffhausen</t>
+          <t>Nîmes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O39" t="n">
         <v>3</v>
       </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N39" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q39" t="n">
         <v>3.75</v>
       </c>
-      <c r="P39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X39" t="n">
         <v>2.6</v>
       </c>
-      <c r="R39" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3.58</v>
-      </c>
       <c r="Y39" t="n">
-        <v>1.77</v>
+        <v>2.45</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.98</v>
+        <v>1.51</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.81</v>
+        <v>4.8</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AC39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD39" t="n">
         <v>1.73</v>
       </c>
-      <c r="AD39" t="n">
-        <v>2</v>
-      </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['64', '82']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>['17', '47', '68']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.95</v>
+        <v>1.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45688.64583333334</v>
@@ -5545,25 +5545,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5571,22 +5571,22 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.83</v>
+        <v>2.33</v>
       </c>
       <c r="M40" t="n">
         <v>3.12</v>
       </c>
       <c r="N40" t="n">
-        <v>2.49</v>
+        <v>3.07</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R40" t="n">
         <v>1.45</v>
@@ -5610,10 +5610,10 @@
         <v>3</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AA40" t="n">
         <v>4</v>
@@ -5622,19 +5622,19 @@
         <v>1.2</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>['12', '41']</t>
+          <t>['9']</t>
         </is>
       </c>
       <c r="AG40" t="n">
@@ -5647,7 +5647,7 @@
         <v>1.8</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45688.64583333334</v>
@@ -5674,25 +5674,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>FC Schaffhausen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.43</v>
+        <v>4.1</v>
       </c>
       <c r="M41" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N41" t="n">
-        <v>2.7</v>
+        <v>1.77</v>
       </c>
       <c r="O41" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="P41" t="n">
         <v>2.2</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="R41" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S41" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="T41" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U41" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="V41" t="n">
         <v>1.01</v>
       </c>
       <c r="W41" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="X41" t="n">
-        <v>3.92</v>
+        <v>3.58</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AB41" t="n">
         <v>1.33</v>
       </c>
       <c r="AC41" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>['64', '82']</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>['17', '47', '68']</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ41" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>['32']</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45688.64583333334</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,25 +5803,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G42" t="n">
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="M42" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>3.07</v>
+        <v>2.7</v>
       </c>
       <c r="O42" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="R42" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U42" t="n">
         <v>1.45</v>
       </c>
-      <c r="S42" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.32</v>
-      </c>
       <c r="V42" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X42" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB42" t="n">
         <v>1.33</v>
       </c>
-      <c r="X42" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Z42" t="n">
+      <c r="AC42" t="n">
         <v>1.62</v>
       </c>
-      <c r="AA42" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AD42" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>['9']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45688.64583333334</v>
@@ -5932,25 +5932,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -5958,34 +5958,34 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="M43" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="N43" t="n">
-        <v>3.71</v>
+        <v>3.97</v>
       </c>
       <c r="O43" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="P43" t="n">
         <v>2</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="R43" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S43" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="T43" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="U43" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V43" t="n">
         <v>1.06</v>
@@ -5997,10 +5997,10 @@
         <v>2.88</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AA43" t="n">
         <v>4</v>
@@ -6009,32 +6009,32 @@
         <v>1.2</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>['10', '76', '85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AJ43" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45688.64583333334</v>
@@ -6061,25 +6061,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -6087,49 +6087,49 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="M44" t="n">
-        <v>3.15</v>
+        <v>3.36</v>
       </c>
       <c r="N44" t="n">
-        <v>3.97</v>
+        <v>4.24</v>
       </c>
       <c r="O44" t="n">
         <v>2.5</v>
       </c>
       <c r="P44" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="R44" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S44" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="T44" t="n">
-        <v>3.26</v>
+        <v>3.14</v>
       </c>
       <c r="U44" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V44" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W44" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X44" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AA44" t="n">
         <v>4</v>
@@ -6138,32 +6138,32 @@
         <v>1.2</v>
       </c>
       <c r="AC44" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['62', '78', '90+5']</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '30']</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AI44" t="n">
         <v>1.57</v>
       </c>
       <c r="AJ44" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45688.64583333334</v>
@@ -6190,75 +6190,75 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="n">
         <v>3</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P45" t="n">
         <v>2</v>
       </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="M45" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="N45" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="O45" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q45" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="R45" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S45" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="T45" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="U45" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V45" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W45" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X45" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AA45" t="n">
         <v>4</v>
@@ -6267,32 +6267,32 @@
         <v>1.2</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>['62', '78', '90+5']</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>['27', '30']</t>
+          <t>['10', '76', '85']</t>
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AJ45" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45688.64583333334</v>
@@ -6319,25 +6319,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Nîmes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -6345,62 +6345,62 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.22</v>
+        <v>2.83</v>
       </c>
       <c r="M46" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="N46" t="n">
-        <v>3.25</v>
+        <v>2.49</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
       </c>
       <c r="P46" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X46" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD46" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q46" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S46" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T46" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X46" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AE46" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6408,20 +6408,20 @@
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['12', '41']</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AI46" t="n">
         <v>1.8</v>
       </c>
       <c r="AJ46" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45688.64583333334</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,16 +6577,16 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Martigues</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
@@ -6595,7 +6595,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -6603,83 +6603,83 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.8</v>
+        <v>1.35</v>
       </c>
       <c r="M48" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="N48" t="n">
-        <v>3.95</v>
+        <v>8.1</v>
       </c>
       <c r="O48" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="P48" t="n">
         <v>2.3</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="R48" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S48" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T48" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="U48" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V48" t="n">
         <v>1.04</v>
       </c>
       <c r="W48" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X48" t="n">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="Y48" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD48" t="n">
         <v>1.67</v>
       </c>
-      <c r="Z48" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>['51', '77']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.62</v>
+        <v>1.32</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45688.66666666666</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,16 +6706,16 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H49" t="n">
         <v>1</v>
@@ -6724,7 +6724,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -6732,83 +6732,83 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="M49" t="n">
-        <v>3.48</v>
+        <v>3.85</v>
       </c>
       <c r="N49" t="n">
-        <v>3.56</v>
+        <v>3.95</v>
       </c>
       <c r="O49" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="P49" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="Q49" t="n">
         <v>4</v>
       </c>
       <c r="R49" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="S49" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="T49" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="U49" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V49" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W49" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="X49" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.07</v>
+        <v>1.67</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AA49" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>['90+1']</t>
+          <t>['51', '77']</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>['46']</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AJ49" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45688.66666666666</v>
@@ -6835,19 +6835,19 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
         <v>1</v>
@@ -6861,80 +6861,80 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.12</v>
+        <v>2.74</v>
       </c>
       <c r="M50" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="N50" t="n">
-        <v>3.13</v>
+        <v>2.84</v>
       </c>
       <c r="O50" t="n">
         <v>3.25</v>
       </c>
       <c r="P50" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="R50" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S50" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T50" t="n">
         <v>3.4</v>
       </c>
       <c r="U50" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V50" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W50" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="X50" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="Y50" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="AA50" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AJ50" t="n">
         <v>2.2</v>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6979,7 +6979,7 @@
         <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -6990,83 +6990,83 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.74</v>
+        <v>2.06</v>
       </c>
       <c r="M51" t="n">
-        <v>2.98</v>
+        <v>3.48</v>
       </c>
       <c r="N51" t="n">
-        <v>2.84</v>
+        <v>3.56</v>
       </c>
       <c r="O51" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="P51" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="R51" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="S51" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="T51" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="U51" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="V51" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="W51" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="X51" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.48</v>
+        <v>2.07</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="AA51" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AD51" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>['90+1']</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>['46']</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH51" t="n">
         <v>1.73</v>
       </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>['11']</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>['90+5']</t>
-        </is>
-      </c>
-      <c r="AG51" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AI51" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AJ51" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45688.66666666666</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,19 +7093,19 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>KMSK Deinze</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Martigues</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -7115,65 +7115,65 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7182,20 +7182,20 @@
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45688.66666666666</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,25 +7222,25 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -7248,83 +7248,83 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="M53" t="n">
-        <v>5.5</v>
+        <v>3.38</v>
       </c>
       <c r="N53" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="O53" t="n">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="P53" t="n">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="Q53" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="R53" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="S53" t="n">
-        <v>3.75</v>
+        <v>2.4</v>
       </c>
       <c r="T53" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="U53" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="V53" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W53" t="n">
-        <v>1.1</v>
+        <v>1.48</v>
       </c>
       <c r="X53" t="n">
-        <v>7</v>
+        <v>2.65</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.44</v>
+        <v>2.34</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.1</v>
+        <v>4.75</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.65</v>
+        <v>1.18</v>
       </c>
       <c r="AC53" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD53" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD53" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>['48', '56', '60', '69']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>['20', '72']</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AH53" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AJ53" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45688.66666666666</v>
@@ -7351,25 +7351,25 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
         <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -7377,83 +7377,83 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.83</v>
+        <v>2.59</v>
       </c>
       <c r="M54" t="n">
         <v>3.38</v>
       </c>
       <c r="N54" t="n">
-        <v>4.7</v>
+        <v>2.69</v>
       </c>
       <c r="O54" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="P54" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X54" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>['17', '71']</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI54" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q54" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S54" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T54" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X54" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>['77']</t>
-        </is>
-      </c>
-      <c r="AG54" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AJ54" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45688.66666666666</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,109 +7480,109 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="O55" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P55" t="n">
         <v>2</v>
       </c>
-      <c r="H55" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>1</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M55" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N55" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="O55" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P55" t="n">
+      <c r="Q55" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S55" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q55" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S55" t="n">
-        <v>3.55</v>
-      </c>
       <c r="T55" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X55" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ55" t="n">
         <v>2.2</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X55" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>['47', '90+4']</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>['3']</t>
-        </is>
-      </c>
-      <c r="AG55" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>2.8</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45688.66666666666</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,22 +7738,22 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G57" t="n">
+        <v>4</v>
+      </c>
+      <c r="H57" t="n">
         <v>2</v>
       </c>
-      <c r="H57" t="n">
-        <v>1</v>
-      </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
         <v>1</v>
@@ -7764,83 +7764,83 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.59</v>
+        <v>1.4</v>
       </c>
       <c r="M57" t="n">
-        <v>3.38</v>
+        <v>5.5</v>
       </c>
       <c r="N57" t="n">
-        <v>2.69</v>
+        <v>6</v>
       </c>
       <c r="O57" t="n">
-        <v>2.95</v>
+        <v>1.91</v>
       </c>
       <c r="P57" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="R57" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="S57" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="T57" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="U57" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="V57" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W57" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="X57" t="n">
-        <v>3.55</v>
+        <v>7</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.86</v>
+        <v>1.44</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.94</v>
+        <v>2.7</v>
       </c>
       <c r="AA57" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AD57" t="n">
         <v>2.1</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>['17', '71']</t>
+          <t>['48', '56', '60', '69']</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>['12']</t>
+          <t>['20', '72']</t>
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.55</v>
+        <v>2.75</v>
       </c>
       <c r="AI57" t="n">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="AJ57" t="n">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45688.66666666666</v>
@@ -7867,25 +7867,25 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -7893,83 +7893,83 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.6</v>
+        <v>1.53</v>
       </c>
       <c r="M58" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N58" t="n">
-        <v>1.91</v>
+        <v>5.25</v>
       </c>
       <c r="O58" t="n">
-        <v>3.75</v>
+        <v>1.95</v>
       </c>
       <c r="P58" t="n">
         <v>2.5</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.4</v>
+        <v>4.75</v>
       </c>
       <c r="R58" t="n">
         <v>1.25</v>
       </c>
       <c r="S58" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="T58" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X58" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD58" t="n">
         <v>2.1</v>
       </c>
-      <c r="U58" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V58" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W58" t="n">
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>['47', '90+4']</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>['3']</t>
+        </is>
+      </c>
+      <c r="AG58" t="n">
         <v>1.15</v>
       </c>
-      <c r="X58" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE58" t="inlineStr">
-        <is>
-          <t>['43', '48', '72']</t>
-        </is>
-      </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG58" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AH58" t="n">
-        <v>1.25</v>
+        <v>2.4</v>
       </c>
       <c r="AI58" t="n">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="AJ58" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45688.66666666666</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,16 +7996,16 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H59" t="n">
         <v>1</v>
@@ -8022,83 +8022,83 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="M59" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="N59" t="n">
-        <v>3.94</v>
+        <v>3.38</v>
       </c>
       <c r="O59" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="P59" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="R59" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S59" t="n">
         <v>3</v>
       </c>
       <c r="T59" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="U59" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V59" t="n">
         <v>1.05</v>
       </c>
       <c r="W59" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X59" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.29</v>
+        <v>2.06</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="AB59" t="n">
         <v>1.38</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AD59" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>['27', '60']</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>['54']</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AI59" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AJ59" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AK59" s="3" t="n">
         <v>45688.66666666666</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,22 +8125,22 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -8151,65 +8151,65 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.09</v>
+        <v>3.6</v>
       </c>
       <c r="M60" t="n">
-        <v>9.92</v>
+        <v>4</v>
       </c>
       <c r="N60" t="n">
-        <v>9.99</v>
+        <v>1.91</v>
       </c>
       <c r="O60" t="n">
-        <v>1.22</v>
+        <v>3.75</v>
       </c>
       <c r="P60" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="Q60" t="n">
-        <v>21</v>
+        <v>2.4</v>
       </c>
       <c r="R60" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S60" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W60" t="n">
         <v>1.15</v>
       </c>
-      <c r="S60" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="T60" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U60" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V60" t="n">
-        <v>0</v>
-      </c>
-      <c r="W60" t="n">
-        <v>1.03</v>
-      </c>
       <c r="X60" t="n">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="Z60" t="n">
-        <v>3.64</v>
+        <v>2.7</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.95</v>
+        <v>1.44</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.3</v>
+        <v>2.63</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>['39', '45+2', '51', '64', '90+2']</t>
+          <t>['43', '48', '72']</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -8218,16 +8218,16 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="AH60" t="n">
-        <v>11</v>
+        <v>1.25</v>
       </c>
       <c r="AI60" t="n">
-        <v>1.07</v>
+        <v>2.3</v>
       </c>
       <c r="AJ60" t="n">
-        <v>9</v>
+        <v>1.57</v>
       </c>
       <c r="AK60" s="3" t="n">
         <v>45688.66666666666</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,109 +8254,109 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KMSK Deinze</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AI61" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK61" s="3" t="n">
         <v>45688.66666666666</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,23 +8383,23 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G62" t="n">
+        <v>5</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
         <v>2</v>
       </c>
-      <c r="H62" t="n">
-        <v>1</v>
-      </c>
-      <c r="I62" t="n">
-        <v>1</v>
-      </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
@@ -8409,83 +8409,83 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.96</v>
+        <v>1.09</v>
       </c>
       <c r="M62" t="n">
-        <v>3.65</v>
+        <v>9.92</v>
       </c>
       <c r="N62" t="n">
-        <v>3.38</v>
+        <v>9.99</v>
       </c>
       <c r="O62" t="n">
-        <v>2.55</v>
+        <v>1.22</v>
       </c>
       <c r="P62" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.7</v>
+        <v>21</v>
       </c>
       <c r="R62" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="T62" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="U62" t="n">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="V62" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="X62" t="n">
-        <v>3.75</v>
+        <v>9</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.06</v>
+        <v>3.64</v>
       </c>
       <c r="AA62" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC62" t="n">
         <v>2.95</v>
       </c>
-      <c r="AB62" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AD62" t="n">
-        <v>2.15</v>
+        <v>1.3</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>['27', '60']</t>
+          <t>['39', '45+2', '51', '64', '90+2']</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.72</v>
+        <v>11</v>
       </c>
       <c r="AI62" t="n">
-        <v>1.73</v>
+        <v>1.07</v>
       </c>
       <c r="AJ62" t="n">
-        <v>2.25</v>
+        <v>9</v>
       </c>
       <c r="AK62" s="3" t="n">
         <v>45688.66666666666</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,54 +8641,54 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G64" t="n">
         <v>1</v>
       </c>
       <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M64" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N64" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O64" t="n">
+        <v>3</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q64" t="n">
         <v>4</v>
       </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L64" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="M64" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="N64" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="O64" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P64" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R64" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S64" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T64" t="n">
         <v>3.4</v>
@@ -8697,53 +8697,53 @@
         <v>1.3</v>
       </c>
       <c r="V64" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W64" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="X64" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AA64" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AC64" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD64" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>['37']</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG64" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI64" t="n">
         <v>1.73</v>
       </c>
-      <c r="AE64" t="inlineStr">
-        <is>
-          <t>['90+1']</t>
-        </is>
-      </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>['56', '70', '82', '90+6']</t>
-        </is>
-      </c>
-      <c r="AG64" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AJ64" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AK64" s="3" t="n">
         <v>45688.6875</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,109 +8770,109 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H65" t="n">
         <v>1</v>
       </c>
       <c r="I65" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="M65" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N65" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="O65" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P65" t="n">
         <v>2</v>
       </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L65" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="M65" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N65" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="O65" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P65" t="n">
-        <v>2.4</v>
-      </c>
       <c r="Q65" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="R65" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="S65" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T65" t="n">
         <v>3.4</v>
       </c>
-      <c r="T65" t="n">
-        <v>2.43</v>
-      </c>
       <c r="U65" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="V65" t="n">
         <v>1.01</v>
       </c>
       <c r="W65" t="n">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="X65" t="n">
-        <v>4.33</v>
+        <v>2.8</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.19</v>
+        <v>1.62</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.5</v>
+        <v>1.02</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.42</v>
+        <v>1.02</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AD65" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>['5', '45+5', '50', '80']</t>
+          <t>['19', '49']</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AH65" t="n">
-        <v>2.58</v>
+        <v>1.73</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AJ65" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AK65" s="3" t="n">
         <v>45688.6875</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,19 +8899,19 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G66" t="n">
         <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
         <v>1</v>
@@ -8925,61 +8925,61 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="M66" t="n">
-        <v>2.91</v>
+        <v>3.54</v>
       </c>
       <c r="N66" t="n">
-        <v>3.32</v>
+        <v>2.94</v>
       </c>
       <c r="O66" t="n">
+        <v>3</v>
+      </c>
+      <c r="P66" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S66" t="n">
+        <v>3</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X66" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA66" t="n">
         <v>3.1</v>
       </c>
-      <c r="P66" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R66" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S66" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T66" t="n">
-        <v>3</v>
-      </c>
-      <c r="U66" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V66" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W66" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X66" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AB66" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AC66" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
@@ -8988,20 +8988,20 @@
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AI66" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AJ66" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AK66" s="3" t="n">
         <v>45688.6875</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,54 +9028,54 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="M67" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N67" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O67" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P67" t="n">
         <v>2</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="n">
-        <v>2</v>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="M67" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="N67" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="O67" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P67" t="n">
-        <v>2.05</v>
       </c>
       <c r="Q67" t="n">
         <v>3.75</v>
       </c>
       <c r="R67" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S67" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T67" t="n">
         <v>3.4</v>
@@ -9084,53 +9084,53 @@
         <v>1.3</v>
       </c>
       <c r="V67" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W67" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X67" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AA67" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AC67" t="n">
         <v>1.91</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>['13', '26']</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AI67" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AJ67" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AK67" s="3" t="n">
         <v>45688.6875</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,22 +9157,22 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -9183,83 +9183,83 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.78</v>
+        <v>2.36</v>
       </c>
       <c r="M68" t="n">
-        <v>3.24</v>
+        <v>2.97</v>
       </c>
       <c r="N68" t="n">
-        <v>4.37</v>
+        <v>2.95</v>
       </c>
       <c r="O68" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="P68" t="n">
         <v>2</v>
       </c>
       <c r="Q68" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="R68" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S68" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T68" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U68" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V68" t="n">
         <v>1.01</v>
       </c>
       <c r="W68" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="X68" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.02</v>
+        <v>3.45</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="AC68" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>['19', '49']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="AI68" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AJ68" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="AK68" s="3" t="n">
         <v>45688.6875</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,22 +9286,22 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="G69" t="n">
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -9312,83 +9312,83 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="M69" t="n">
-        <v>3.54</v>
+        <v>2.89</v>
       </c>
       <c r="N69" t="n">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="O69" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P69" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q69" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S69" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T69" t="n">
         <v>3.4</v>
       </c>
-      <c r="R69" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S69" t="n">
-        <v>3</v>
-      </c>
-      <c r="T69" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U69" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="V69" t="n">
         <v>1.04</v>
       </c>
       <c r="W69" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="X69" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.74</v>
+        <v>2.25</v>
       </c>
       <c r="Z69" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AA69" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AD69" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['56', '70', '82', '90+6']</t>
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AI69" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AJ69" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AK69" s="3" t="n">
         <v>45688.6875</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,25 +9415,25 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" t="n">
         <v>2</v>
       </c>
-      <c r="H70" t="n">
-        <v>1</v>
-      </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -9441,77 +9441,77 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="M70" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="N70" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="O70" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P70" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S70" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W70" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X70" t="n">
         <v>2.95</v>
       </c>
-      <c r="N70" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O70" t="n">
-        <v>3</v>
-      </c>
-      <c r="P70" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R70" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S70" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T70" t="n">
-        <v>3</v>
-      </c>
-      <c r="U70" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V70" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W70" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X70" t="n">
-        <v>3.25</v>
-      </c>
       <c r="Y70" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AA70" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AD70" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>['18', '75']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>['68']</t>
+          <t>['13', '26']</t>
         </is>
       </c>
       <c r="AG70" t="n">
         <v>1.34</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AI70" t="n">
         <v>1.8</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,109 +9544,109 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H71" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M71" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N71" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O71" t="n">
         <v>3</v>
       </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>1</v>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L71" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="M71" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="N71" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="O71" t="n">
+      <c r="P71" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S71" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W71" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X71" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA71" t="n">
         <v>3.2</v>
       </c>
-      <c r="P71" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R71" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S71" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T71" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U71" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V71" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W71" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X71" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y71" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z71" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AA71" t="n">
-        <v>4.33</v>
-      </c>
       <c r="AB71" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AD71" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>['18', '75']</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>['68']</t>
+        </is>
+      </c>
+      <c r="AG71" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI71" t="n">
         <v>1.8</v>
       </c>
-      <c r="AE71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF71" t="inlineStr">
-        <is>
-          <t>['42', '62', '90']</t>
-        </is>
-      </c>
-      <c r="AG71" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH71" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI71" t="n">
-        <v>2</v>
-      </c>
       <c r="AJ71" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AK71" s="3" t="n">
         <v>45688.6875</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,25 +9673,25 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -9699,58 +9699,58 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="M72" t="n">
-        <v>2.97</v>
+        <v>3.24</v>
       </c>
       <c r="N72" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="O72" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S72" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T72" t="n">
         <v>3.1</v>
       </c>
-      <c r="P72" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R72" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S72" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T72" t="n">
-        <v>3.25</v>
-      </c>
       <c r="U72" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V72" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W72" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="X72" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="Y72" t="n">
         <v>2.25</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AA72" t="n">
-        <v>3.45</v>
+        <v>4.33</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AD72" t="n">
         <v>1.8</v>
@@ -9762,20 +9762,20 @@
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['42', '62', '90']</t>
         </is>
       </c>
       <c r="AG72" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AH72" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AI72" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AJ72" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AK72" s="3" t="n">
         <v>45688.6875</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,25 +9802,25 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H73" t="n">
         <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -9828,83 +9828,83 @@
         </is>
       </c>
       <c r="L73" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M73" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N73" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="O73" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P73" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S73" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T73" t="n">
         <v>2.43</v>
       </c>
-      <c r="M73" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="N73" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O73" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P73" t="n">
+      <c r="U73" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W73" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X73" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD73" t="n">
         <v>2</v>
       </c>
-      <c r="Q73" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R73" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S73" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T73" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U73" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V73" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W73" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X73" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y73" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Z73" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA73" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB73" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC73" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD73" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '45+5', '50', '80']</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="AG73" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.57</v>
+        <v>2.58</v>
       </c>
       <c r="AI73" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AJ73" t="n">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="AK73" s="3" t="n">
         <v>45688.6875</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,19 +9931,19 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G74" t="n">
         <v>1</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" t="n">
         <v>1</v>
@@ -9957,83 +9957,83 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="M74" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="N74" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="O74" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S74" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T74" t="n">
         <v>3</v>
       </c>
-      <c r="P74" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>4</v>
-      </c>
-      <c r="R74" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S74" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T74" t="n">
+      <c r="U74" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V74" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W74" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X74" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA74" t="n">
         <v>3.4</v>
       </c>
-      <c r="U74" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V74" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W74" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X74" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z74" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA74" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AB74" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AC74" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD74" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AG74" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AH74" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AI74" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AJ74" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AK74" s="3" t="n">
         <v>45688.6875</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,25 +10189,25 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -10215,83 +10215,83 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.23</v>
+        <v>4.02</v>
       </c>
       <c r="M76" t="n">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="N76" t="n">
-        <v>3.14</v>
+        <v>1.82</v>
       </c>
       <c r="O76" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="P76" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="R76" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S76" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="T76" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U76" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="V76" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W76" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="X76" t="n">
-        <v>3.52</v>
+        <v>4.33</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AA76" t="n">
-        <v>3.26</v>
+        <v>2.7</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AD76" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1', '61']</t>
         </is>
       </c>
       <c r="AG76" t="n">
-        <v>1.43</v>
+        <v>1.93</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.52</v>
+        <v>1.23</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="AJ76" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AK76" s="3" t="n">
         <v>45688.69791666666</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,109 +10318,109 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G77" t="n">
         <v>1</v>
       </c>
       <c r="H77" t="n">
+        <v>2</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>2</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="M77" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N77" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="O77" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P77" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R77" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S77" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T77" t="n">
         <v>3</v>
       </c>
-      <c r="I77" t="n">
-        <v>1</v>
-      </c>
-      <c r="J77" t="n">
-        <v>1</v>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L77" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="M77" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="N77" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="O77" t="n">
+      <c r="U77" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V77" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W77" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X77" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>['13', '45+4']</t>
+        </is>
+      </c>
+      <c r="AG77" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ77" t="n">
         <v>2.75</v>
-      </c>
-      <c r="P77" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R77" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S77" t="n">
-        <v>3</v>
-      </c>
-      <c r="T77" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U77" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V77" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W77" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X77" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y77" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z77" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AA77" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB77" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC77" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD77" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE77" t="inlineStr">
-        <is>
-          <t>['34']</t>
-        </is>
-      </c>
-      <c r="AF77" t="inlineStr">
-        <is>
-          <t>['36', '63', '90+3']</t>
-        </is>
-      </c>
-      <c r="AG77" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH77" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AI77" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ77" t="n">
-        <v>2.38</v>
       </c>
       <c r="AK77" s="3" t="n">
         <v>45688.69791666666</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,25 +10447,25 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -10473,83 +10473,83 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>4.02</v>
+        <v>2.23</v>
       </c>
       <c r="M78" t="n">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="N78" t="n">
-        <v>1.82</v>
+        <v>3.14</v>
       </c>
       <c r="O78" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="P78" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q78" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="R78" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S78" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="T78" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U78" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="V78" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W78" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="X78" t="n">
-        <v>4.33</v>
+        <v>3.52</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.7</v>
+        <v>3.26</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AC78" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AD78" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AE78" t="inlineStr">
         <is>
+          <t>['6']</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF78" t="inlineStr">
-        <is>
-          <t>['1', '61']</t>
-        </is>
-      </c>
       <c r="AG78" t="n">
-        <v>1.93</v>
+        <v>1.43</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.23</v>
+        <v>1.52</v>
       </c>
       <c r="AI78" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AJ78" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AK78" s="3" t="n">
         <v>45688.69791666666</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,109 +10576,109 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G79" t="n">
         <v>1</v>
       </c>
       <c r="H79" t="n">
+        <v>3</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M79" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N79" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="O79" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P79" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S79" t="n">
+        <v>3</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V79" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W79" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X79" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y79" t="n">
         <v>2</v>
       </c>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" t="n">
-        <v>2</v>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L79" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="M79" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N79" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="O79" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P79" t="n">
+      <c r="Z79" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD79" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q79" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R79" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S79" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T79" t="n">
-        <v>3</v>
-      </c>
-      <c r="U79" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V79" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W79" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X79" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA79" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB79" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC79" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
         <is>
-          <t>['13', '45+4']</t>
+          <t>['36', '63', '90+3']</t>
         </is>
       </c>
       <c r="AG79" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AI79" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AJ79" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AK79" s="3" t="n">
         <v>45688.69791666666</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,22 +10705,22 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H80" t="n">
         <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -10731,83 +10731,83 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>3</v>
+        <v>2.06</v>
       </c>
       <c r="M80" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="N80" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="O80" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P80" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S80" t="n">
         <v>2.5</v>
       </c>
-      <c r="O80" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P80" t="n">
+      <c r="T80" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V80" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W80" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X80" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC80" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q80" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R80" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S80" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T80" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U80" t="n">
+      <c r="AD80" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>['39', '78']</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="AG80" t="n">
         <v>1.25</v>
       </c>
-      <c r="V80" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W80" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X80" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Y80" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Z80" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA80" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB80" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC80" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD80" t="n">
+      <c r="AH80" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI80" t="n">
         <v>1.67</v>
       </c>
-      <c r="AE80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF80" t="inlineStr">
-        <is>
-          <t>['78']</t>
-        </is>
-      </c>
-      <c r="AG80" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH80" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI80" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ80" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="AK80" s="3" t="n">
         <v>45688.70833333334</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,22 +10834,22 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
         <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -10860,83 +10860,83 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.06</v>
+        <v>3</v>
       </c>
       <c r="M81" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="N81" t="n">
-        <v>3.76</v>
+        <v>2.5</v>
       </c>
       <c r="O81" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="P81" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="R81" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S81" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T81" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V81" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W81" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X81" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Z81" t="n">
         <v>1.5</v>
       </c>
-      <c r="S81" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T81" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U81" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V81" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W81" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X81" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AA81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC81" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="AG81" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ81" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AD81" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE81" t="inlineStr">
-        <is>
-          <t>['39', '78']</t>
-        </is>
-      </c>
-      <c r="AF81" t="inlineStr">
-        <is>
-          <t>['90+3']</t>
-        </is>
-      </c>
-      <c r="AG81" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH81" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AI81" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ81" t="n">
-        <v>2.6</v>
       </c>
       <c r="AK81" s="3" t="n">
         <v>45688.70833333334</v>
